--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ45"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111596832</v>
+        <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>92134</v>
+        <v>87422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1106</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen 139 m NE, Upl</t>
+          <t>Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654305</v>
+        <v>654218</v>
       </c>
       <c r="R2" t="n">
-        <v>6690856</v>
+        <v>6691076</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,24 +765,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596832</t>
+          <t>https://artportalen.se/Sighting/137373015</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111596833</v>
+        <v>111596832</v>
       </c>
       <c r="B3" t="n">
         <v>92134</v>
@@ -829,14 +816,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen 319 m N, Upl</t>
+          <t>Björkmossen 139 m NE, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654190</v>
+        <v>654305</v>
       </c>
       <c r="R3" t="n">
-        <v>6691090</v>
+        <v>6690856</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +855,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +865,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +891,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596833</t>
+          <t>https://artportalen.se/Sighting/111596832</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111596831</v>
+        <v>111596833</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,14 +931,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen 304 m N, Upl</t>
+          <t>Björkmossen 319 m N, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654195</v>
+        <v>654190</v>
       </c>
       <c r="R4" t="n">
-        <v>6691076</v>
+        <v>6691090</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +970,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +980,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,16 +1006,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596831</t>
+          <t>https://artportalen.se/Sighting/111596833</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111210851</v>
+        <v>111596831</v>
       </c>
       <c r="B5" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,44 +1023,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen 168 m N, Upl</t>
+          <t>Björkmossen 304 m N, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654479</v>
+        <v>654195</v>
       </c>
       <c r="R5" t="n">
-        <v>6690762</v>
+        <v>6691076</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1080,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,57 +1121,61 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210851</t>
+          <t>https://artportalen.se/Sighting/111596831</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111596825</v>
+        <v>111210851</v>
       </c>
       <c r="B6" t="n">
-        <v>91680</v>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkmossen 246 m E, Upl</t>
+          <t>Björkmossen 168 m N, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654442</v>
+        <v>654479</v>
       </c>
       <c r="R6" t="n">
-        <v>6690766</v>
+        <v>6690762</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1199,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,57 +1240,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596825</t>
+          <t>https://artportalen.se/Sighting/111210851</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111596836</v>
+        <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>93209</v>
+        <v>96622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkmossen 206 m E, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654400</v>
+        <v>654314</v>
       </c>
       <c r="R7" t="n">
-        <v>6690787</v>
+        <v>6690906</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,22 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,75 +1325,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596836</t>
+          <t>https://artportalen.se/Sighting/137366594</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111596838</v>
+        <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>93209</v>
+        <v>96622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>2812</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkmossen 141 m NE, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654275</v>
+        <v>654372</v>
       </c>
       <c r="R8" t="n">
-        <v>6690886</v>
+        <v>6691006</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,112 +1413,88 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Luktar just ingenting. Smakar gammalt papper typ. Tar en liten bit från två olika fruktkroppar men kan inte känna nån skarp smak. Färgar av sig på fingrarna. Utifrån miljön bör det ändå vara skarp dropptaggsvamp.</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596838</t>
+          <t>https://artportalen.se/Sighting/137367792</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111596844</v>
+        <v>111596825</v>
       </c>
       <c r="B9" t="n">
-        <v>93215</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4368</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkmossen 284 m E, Upl</t>
+          <t>Björkmossen 246 m E, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654479</v>
+        <v>654442</v>
       </c>
       <c r="R9" t="n">
-        <v>6690759</v>
+        <v>6690766</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rätt stark men angenäm doft av bittermandel.</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1542,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1619,38 +1559,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596844</t>
+          <t>https://artportalen.se/Sighting/111596825</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111596830</v>
+        <v>111596836</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,14 +1599,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkmossen 277 m N, Upl</t>
+          <t>Björkmossen 206 m E, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654228</v>
+        <v>654400</v>
       </c>
       <c r="R10" t="n">
-        <v>6691046</v>
+        <v>6690787</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1698,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,6 +1657,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1734,16 +1675,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596830</t>
+          <t>https://artportalen.se/Sighting/111596836</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111596843</v>
+        <v>111596838</v>
       </c>
       <c r="B11" t="n">
-        <v>93223</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,48 +1692,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkmossen 282 m E, Upl</t>
+          <t>Björkmossen 141 m NE, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654477</v>
+        <v>654275</v>
       </c>
       <c r="R11" t="n">
-        <v>6690758</v>
+        <v>6690886</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,20 +1764,21 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Väldigt svag doft.</t>
+          <t>Luktar just ingenting. Smakar gammalt papper typ. Tar en liten bit från två olika fruktkroppar men kan inte känna nån skarp smak. Färgar av sig på fingrarna. Utifrån miljön bör det ändå vara skarp dropptaggsvamp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1862,16 +1796,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596843</t>
+          <t>https://artportalen.se/Sighting/111596838</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111596840</v>
+        <v>111596844</v>
       </c>
       <c r="B12" t="n">
-        <v>93233</v>
+        <v>93215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,37 +1813,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björkmossen 180 m NE, Upl</t>
+          <t>Björkmossen 284 m E, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654329</v>
+        <v>654479</v>
       </c>
       <c r="R12" t="n">
-        <v>6690891</v>
+        <v>6690759</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1941,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1893,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fuktig mark med nästan bara gran.</t>
+          <t>Rätt stark men angenäm doft av bittermandel.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,6 +1907,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1982,65 +1925,57 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596840</t>
+          <t>https://artportalen.se/Sighting/111596844</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111596842</v>
+        <v>111596830</v>
       </c>
       <c r="B13" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkmossen 289 m NE, Upl</t>
+          <t>Björkmossen 277 m N, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654342</v>
+        <v>654228</v>
       </c>
       <c r="R13" t="n">
-        <v>6691020</v>
+        <v>6691046</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2069,7 +2004,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2079,12 +2014,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Fuktig mark med mest gran.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,16 +2040,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596842</t>
+          <t>https://artportalen.se/Sighting/111596830</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111596822</v>
+        <v>111596843</v>
       </c>
       <c r="B14" t="n">
-        <v>75428</v>
+        <v>93223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,40 +2057,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>5448</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björkmossen 300 m SE, Upl</t>
+          <t>Björkmossen 282 m E, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654488</v>
+        <v>654477</v>
       </c>
       <c r="R14" t="n">
-        <v>6690707</v>
+        <v>6690758</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2189,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2137,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Väldigt svag doft.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,66 +2168,57 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596822</t>
+          <t>https://artportalen.se/Sighting/111596843</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111210764</v>
+        <v>111596840</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>93233</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björkmossen 222 m NW, Upl</t>
+          <t>Björkmossen 180 m NE, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654453</v>
+        <v>654329</v>
       </c>
       <c r="R15" t="n">
-        <v>6690811</v>
+        <v>6690891</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2308,22 +2242,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fuktig mark med nästan bara gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,63 +2288,62 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210764</t>
+          <t>https://artportalen.se/Sighting/111596840</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111596815</v>
+        <v>111596842</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>93233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björkmossen 262 m E, Upl</t>
+          <t>Björkmossen 289 m NE, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654455</v>
+        <v>654342</v>
       </c>
       <c r="R16" t="n">
-        <v>6690804</v>
+        <v>6691020</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2437,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,7 +2385,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fuktig mark med mest gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,67 +2416,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596815</t>
+          <t>https://artportalen.se/Sighting/111596842</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111210759</v>
+        <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>5179</v>
+        <v>93497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björkmossen 418 m NW, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654327</v>
+        <v>654371</v>
       </c>
       <c r="R17" t="n">
-        <v>6690973</v>
+        <v>6691059</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2557,22 +2487,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,74 +2507,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210759</t>
+          <t>https://artportalen.se/Sighting/137366053</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111596818</v>
+        <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>58790</v>
+        <v>93497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208245</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björkmossen 269 m N, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654176</v>
+        <v>654219</v>
       </c>
       <c r="R18" t="n">
-        <v>6691040</v>
+        <v>6691055</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2678,22 +2589,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:12</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2708,77 +2609,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596818</t>
+          <t>https://artportalen.se/Sighting/137367674</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111210904</v>
+        <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>106244</v>
+        <v>93497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Björkmossen 185 m NW, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654440</v>
+        <v>654339</v>
       </c>
       <c r="R19" t="n">
-        <v>6690768</v>
+        <v>6691037</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2802,22 +2691,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,77 +2711,68 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210904</t>
+          <t>https://artportalen.se/Sighting/137367749</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111210908</v>
+        <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>106244</v>
+        <v>93497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björkmossen 238 m NW, Upl</t>
+          <t>Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654384</v>
+        <v>654218</v>
       </c>
       <c r="R20" t="n">
-        <v>6690798</v>
+        <v>6691048</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2926,22 +2796,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2950,83 +2810,75 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210908</t>
+          <t>https://artportalen.se/Sighting/137373016</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111596895</v>
+        <v>111596822</v>
       </c>
       <c r="B21" t="n">
-        <v>106244</v>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Björkmossen 238 m E, Upl</t>
+          <t>Björkmossen 300 m SE, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654433</v>
+        <v>654488</v>
       </c>
       <c r="R21" t="n">
-        <v>6690769</v>
+        <v>6690707</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3055,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,12 +2917,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Cirka.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3096,16 +2943,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596895</t>
+          <t>https://artportalen.se/Sighting/111596822</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111596897</v>
+        <v>111210764</v>
       </c>
       <c r="B22" t="n">
-        <v>106244</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3113,49 +2960,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björkmossen 227 m E, Upl</t>
+          <t>Björkmossen 222 m NW, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>654422</v>
+        <v>654453</v>
       </c>
       <c r="R22" t="n">
-        <v>6690769</v>
+        <v>6690811</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3179,27 +3026,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Uppskattat antal, helt tjockt med plantor så går ej att räkna.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,16 +3067,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596897</t>
+          <t>https://artportalen.se/Sighting/111210764</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111596900</v>
+        <v>111596815</v>
       </c>
       <c r="B23" t="n">
-        <v>106244</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3242,49 +3084,49 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björkmossen 230 m E, Upl</t>
+          <t>Björkmossen 262 m E, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654425</v>
+        <v>654455</v>
       </c>
       <c r="R23" t="n">
-        <v>6690762</v>
+        <v>6690804</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3313,7 +3155,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3323,12 +3165,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Uppskattat antal.</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,38 +3191,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596900</t>
+          <t>https://artportalen.se/Sighting/111596815</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111210898</v>
+        <v>111210759</v>
       </c>
       <c r="B24" t="n">
-        <v>102241</v>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3396,20 +3233,25 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björkmossen 182 m N, Upl</t>
+          <t>Björkmossen 418 m NW, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654474</v>
+        <v>654327</v>
       </c>
       <c r="R24" t="n">
-        <v>6690775</v>
+        <v>6690973</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3438,7 +3280,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3448,7 +3290,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3474,58 +3316,63 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210898</t>
+          <t>https://artportalen.se/Sighting/111210759</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111210899</v>
+        <v>111596818</v>
       </c>
       <c r="B25" t="n">
-        <v>102241</v>
+        <v>58790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>208245</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Björkmossen 197 m NW, Upl</t>
+          <t>Björkmossen 269 m N, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654443</v>
+        <v>654176</v>
       </c>
       <c r="R25" t="n">
-        <v>6690782</v>
+        <v>6691040</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3549,22 +3396,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3590,66 +3437,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210899</t>
+          <t>https://artportalen.se/Sighting/111596818</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111210902</v>
+        <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>102241</v>
+        <v>111404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>220240</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Björkmossen 581 m NW, Upl</t>
+          <t>Storvreten, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654185</v>
+        <v>654327</v>
       </c>
       <c r="R26" t="n">
-        <v>6691078</v>
+        <v>6690882</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3673,22 +3508,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:08</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:09</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3703,54 +3528,54 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210902</t>
+          <t>https://artportalen.se/Sighting/137366475</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111210903</v>
+        <v>111210904</v>
       </c>
       <c r="B27" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3763,17 +3588,17 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Björkmossen 177 m N, Upl</t>
+          <t>Björkmossen 185 m NW, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654479</v>
+        <v>654440</v>
       </c>
       <c r="R27" t="n">
-        <v>6690771</v>
+        <v>6690768</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3802,7 +3627,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3812,7 +3637,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3838,58 +3663,66 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210903</t>
+          <t>https://artportalen.se/Sighting/111210904</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111596856</v>
+        <v>111210908</v>
       </c>
       <c r="B28" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Björkmossen 329 m E, Upl</t>
+          <t>Björkmossen 238 m NW, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654522</v>
+        <v>654384</v>
       </c>
       <c r="R28" t="n">
-        <v>6690735</v>
+        <v>6690798</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3913,22 +3746,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3954,43 +3787,43 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596856</t>
+          <t>https://artportalen.se/Sighting/111210908</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111596859</v>
+        <v>111596895</v>
       </c>
       <c r="B29" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4003,14 +3836,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Björkmossen 311 m SE, Upl</t>
+          <t>Björkmossen 238 m E, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654503</v>
+        <v>654433</v>
       </c>
       <c r="R29" t="n">
-        <v>6690725</v>
+        <v>6690769</v>
       </c>
       <c r="S29" t="n">
         <v>6</v>
@@ -4042,7 +3875,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4052,7 +3885,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Cirka.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4078,43 +3916,43 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596859</t>
+          <t>https://artportalen.se/Sighting/111596895</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111596865</v>
+        <v>111596897</v>
       </c>
       <c r="B30" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4127,17 +3965,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Björkmossen 270 m E, Upl</t>
+          <t>Björkmossen 227 m E, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654464</v>
+        <v>654422</v>
       </c>
       <c r="R30" t="n">
-        <v>6690751</v>
+        <v>6690769</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4166,7 +4004,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4176,7 +4014,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, helt tjockt med plantor så går ej att räkna.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4202,43 +4045,43 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596865</t>
+          <t>https://artportalen.se/Sighting/111596897</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111596867</v>
+        <v>111596900</v>
       </c>
       <c r="B31" t="n">
-        <v>102241</v>
+        <v>106244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4251,17 +4094,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Björkmossen 254 m N, Upl</t>
+          <t>Björkmossen 230 m E, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654194</v>
+        <v>654425</v>
       </c>
       <c r="R31" t="n">
-        <v>6691025</v>
+        <v>6690762</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4290,7 +4133,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4300,7 +4143,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4326,58 +4174,62 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596867</t>
+          <t>https://artportalen.se/Sighting/111596900</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111210888</v>
+        <v>111210898</v>
       </c>
       <c r="B32" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Björkmossen 180 m NW, Upl</t>
+          <t>Björkmossen 182 m N, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654464</v>
+        <v>654474</v>
       </c>
       <c r="R32" t="n">
-        <v>6690771</v>
+        <v>6690775</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4406,7 +4258,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4416,7 +4268,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4442,38 +4294,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210888</t>
+          <t>https://artportalen.se/Sighting/111210898</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111210889</v>
+        <v>111210899</v>
       </c>
       <c r="B33" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4483,17 +4335,17 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Björkmossen 233 m NW, Upl</t>
+          <t>Björkmossen 197 m NW, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654387</v>
+        <v>654443</v>
       </c>
       <c r="R33" t="n">
-        <v>6690793</v>
+        <v>6690782</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4522,7 +4374,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4532,7 +4384,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4558,55 +4410,63 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210889</t>
+          <t>https://artportalen.se/Sighting/111210899</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111210890</v>
+        <v>111210902</v>
       </c>
       <c r="B34" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Björkmossen 282 m NW, Upl</t>
+          <t>Björkmossen 581 m NW, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654381</v>
+        <v>654185</v>
       </c>
       <c r="R34" t="n">
-        <v>6690847</v>
+        <v>6691078</v>
       </c>
       <c r="S34" t="n">
         <v>8</v>
@@ -4638,7 +4498,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4648,7 +4508,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4674,58 +4534,66 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210890</t>
+          <t>https://artportalen.se/Sighting/111210902</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111210891</v>
+        <v>111210903</v>
       </c>
       <c r="B35" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Björkmossen 401 m NW, Upl</t>
+          <t>Björkmossen 177 m N, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654371</v>
+        <v>654479</v>
       </c>
       <c r="R35" t="n">
-        <v>6690973</v>
+        <v>6690771</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4754,7 +4622,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4764,7 +4632,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4790,66 +4658,58 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210891</t>
+          <t>https://artportalen.se/Sighting/111210903</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111210893</v>
+        <v>111596856</v>
       </c>
       <c r="B36" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Björkmossen 506 m NW, Upl</t>
+          <t>Björkmossen 329 m E, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654226</v>
+        <v>654522</v>
       </c>
       <c r="R36" t="n">
-        <v>6691016</v>
+        <v>6690735</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4873,22 +4733,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4914,58 +4774,66 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210893</t>
+          <t>https://artportalen.se/Sighting/111596856</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111210894</v>
+        <v>111596859</v>
       </c>
       <c r="B37" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Björkmossen 579 m NW, Upl</t>
+          <t>Björkmossen 311 m SE, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654181</v>
+        <v>654503</v>
       </c>
       <c r="R37" t="n">
-        <v>6691074</v>
+        <v>6690725</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4989,22 +4857,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5030,43 +4898,43 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210894</t>
+          <t>https://artportalen.se/Sighting/111596859</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111210895</v>
+        <v>111596865</v>
       </c>
       <c r="B38" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5079,17 +4947,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Björkmossen 624 m NW, Upl</t>
+          <t>Björkmossen 270 m E, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654159</v>
+        <v>654464</v>
       </c>
       <c r="R38" t="n">
-        <v>6691112</v>
+        <v>6690751</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5113,22 +4981,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5154,58 +5022,66 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210895</t>
+          <t>https://artportalen.se/Sighting/111596865</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111210896</v>
+        <v>111596867</v>
       </c>
       <c r="B39" t="n">
-        <v>101326</v>
+        <v>102241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björkmossen 188 m NW, Upl</t>
+          <t>Björkmossen 254 m N, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654457</v>
+        <v>654194</v>
       </c>
       <c r="R39" t="n">
-        <v>6690777</v>
+        <v>6691025</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5229,22 +5105,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5270,13 +5146,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111210896</t>
+          <t>https://artportalen.se/Sighting/111596867</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111596850</v>
+        <v>111210888</v>
       </c>
       <c r="B40" t="n">
         <v>101326</v>
@@ -5311,17 +5187,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björkmossen 311 m SE, Upl</t>
+          <t>Björkmossen 180 m NW, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654503</v>
+        <v>654464</v>
       </c>
       <c r="R40" t="n">
-        <v>6690726</v>
+        <v>6690771</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5345,22 +5221,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5386,13 +5262,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596850</t>
+          <t>https://artportalen.se/Sighting/111210888</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111596851</v>
+        <v>111210889</v>
       </c>
       <c r="B41" t="n">
         <v>101326</v>
@@ -5420,32 +5296,24 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björkmossen 266 m E, Upl</t>
+          <t>Björkmossen 233 m NW, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654461</v>
+        <v>654387</v>
       </c>
       <c r="R41" t="n">
-        <v>6690769</v>
+        <v>6690793</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5469,22 +5337,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5510,13 +5378,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596851</t>
+          <t>https://artportalen.se/Sighting/111210889</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111596852</v>
+        <v>111210890</v>
       </c>
       <c r="B42" t="n">
         <v>101326</v>
@@ -5551,17 +5419,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björkmossen 202 m E, Upl</t>
+          <t>Björkmossen 282 m NW, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654397</v>
+        <v>654381</v>
       </c>
       <c r="R42" t="n">
-        <v>6690785</v>
+        <v>6690847</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5585,22 +5453,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5626,13 +5494,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596852</t>
+          <t>https://artportalen.se/Sighting/111210890</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111596853</v>
+        <v>111210891</v>
       </c>
       <c r="B43" t="n">
         <v>101326</v>
@@ -5667,17 +5535,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björkmossen 243 m NE, Upl</t>
+          <t>Björkmossen 401 m NW, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654327</v>
+        <v>654371</v>
       </c>
       <c r="R43" t="n">
-        <v>6690975</v>
+        <v>6690973</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5701,22 +5569,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5742,13 +5610,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596853</t>
+          <t>https://artportalen.se/Sighting/111210891</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111596854</v>
+        <v>111210893</v>
       </c>
       <c r="B44" t="n">
         <v>101326</v>
@@ -5776,24 +5644,32 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björkmossen 296 m NE, Upl</t>
+          <t>Björkmossen 506 m NW, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654358</v>
+        <v>654226</v>
       </c>
       <c r="R44" t="n">
-        <v>6691018</v>
+        <v>6691016</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5817,22 +5693,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5858,13 +5734,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111596854</t>
+          <t>https://artportalen.se/Sighting/111210893</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111596855</v>
+        <v>111210894</v>
       </c>
       <c r="B45" t="n">
         <v>101326</v>
@@ -5899,17 +5775,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björkmossen 242 m NE, Upl</t>
+          <t>Björkmossen 579 m NW, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654233</v>
+        <v>654181</v>
       </c>
       <c r="R45" t="n">
-        <v>6691011</v>
+        <v>6691074</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5933,22 +5809,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5973,6 +5849,950 @@
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210894</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>111210895</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Björkmossen 624 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>654159</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6691112</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210895</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>111210896</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Björkmossen 188 m NW, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>654457</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6690777</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111210896</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>111596850</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Björkmossen 311 m SE, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>654503</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6690726</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596850</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>111596851</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Björkmossen 266 m E, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>654461</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6690769</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596851</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>111596852</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Björkmossen 202 m E, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>654397</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6690785</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596852</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>111596853</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Björkmossen 243 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>654327</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6690975</v>
+      </c>
+      <c r="S51" t="n">
+        <v>6</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596853</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>111596854</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Björkmossen 296 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>654358</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6691018</v>
+      </c>
+      <c r="S52" t="n">
+        <v>8</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111596854</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>111596855</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Björkmossen 242 m NE, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>654233</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6691011</v>
+      </c>
+      <c r="S53" t="n">
+        <v>11</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Tegelsmora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111596855</t>
         </is>
@@ -6024,6 +6844,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>87422</v>
+        <v>87427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>87427</v>
+        <v>87438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>87438</v>
+        <v>87439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>87439</v>
+        <v>87442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2023 artfynd.xlsx
+++ b/artfynd/A 29232-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373015</v>
       </c>
       <c r="B2" t="n">
-        <v>87442</v>
+        <v>87446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>137366594</v>
       </c>
       <c r="B7" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137367792</v>
       </c>
       <c r="B8" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>137366053</v>
       </c>
       <c r="B17" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137367674</v>
       </c>
       <c r="B18" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>137367749</v>
       </c>
       <c r="B19" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>137373016</v>
       </c>
       <c r="B20" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>137366475</v>
       </c>
       <c r="B26" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
